--- a/dados/gerencial/consolidado_gerencial_2019.xlsx
+++ b/dados/gerencial/consolidado_gerencial_2019.xlsx
@@ -494,16 +494,16 @@
         <v>120</v>
       </c>
       <c r="D4" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E4" t="n">
-        <v>524030.77</v>
+        <v>523634.51</v>
       </c>
       <c r="F4" t="n">
-        <v>343426.43</v>
+        <v>341883.15</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>43509</v>
+        <v>43508</v>
       </c>
     </row>
     <row r="5">
@@ -522,13 +522,13 @@
         <v>42</v>
       </c>
       <c r="E5" t="n">
-        <v>513199.21</v>
+        <v>512266.92</v>
       </c>
       <c r="F5" t="n">
-        <v>309481.74</v>
+        <v>309198.01</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>43539</v>
+        <v>43536</v>
       </c>
     </row>
     <row r="6">
@@ -547,13 +547,13 @@
         <v>51</v>
       </c>
       <c r="E6" t="n">
-        <v>519296.89</v>
+        <v>520044.91</v>
       </c>
       <c r="F6" t="n">
-        <v>320970.22</v>
+        <v>319657.46</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>43563</v>
+        <v>43564</v>
       </c>
     </row>
     <row r="7">
@@ -572,13 +572,13 @@
         <v>47</v>
       </c>
       <c r="E7" t="n">
-        <v>572123.7</v>
+        <v>571863.34</v>
       </c>
       <c r="F7" t="n">
-        <v>363573.19</v>
+        <v>361557.91</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>43598</v>
+        <v>43594</v>
       </c>
     </row>
     <row r="8">
@@ -597,13 +597,13 @@
         <v>69</v>
       </c>
       <c r="E8" t="n">
-        <v>604034.5699999999</v>
+        <v>604373.92</v>
       </c>
       <c r="F8" t="n">
-        <v>382839.38</v>
+        <v>381638.76</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>43630</v>
+        <v>43628</v>
       </c>
     </row>
     <row r="9">
@@ -619,13 +619,13 @@
         <v>134</v>
       </c>
       <c r="D9" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E9" t="n">
-        <v>593775.67</v>
+        <v>592434.98</v>
       </c>
       <c r="F9" t="n">
-        <v>379461.63</v>
+        <v>377298.37</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>43661</v>
@@ -647,13 +647,13 @@
         <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>30588.56</v>
+        <v>30496.29</v>
       </c>
       <c r="F10" t="n">
-        <v>17100.01</v>
+        <v>17083.21</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>43661</v>
+        <v>43658</v>
       </c>
     </row>
     <row r="11">
@@ -669,16 +669,16 @@
         <v>143</v>
       </c>
       <c r="D11" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E11" t="n">
-        <v>663450.1800000001</v>
+        <v>664360.64</v>
       </c>
       <c r="F11" t="n">
-        <v>426709.35</v>
+        <v>425887.44</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>43691</v>
+        <v>43690</v>
       </c>
     </row>
     <row r="12">
@@ -697,13 +697,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>62297.85</v>
+        <v>62368.84</v>
       </c>
       <c r="F12" t="n">
-        <v>41398.16</v>
+        <v>39684.52</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>43689</v>
+        <v>43690</v>
       </c>
     </row>
     <row r="13">
@@ -719,16 +719,16 @@
         <v>162</v>
       </c>
       <c r="D13" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E13" t="n">
-        <v>721982.53</v>
+        <v>721536.47</v>
       </c>
       <c r="F13" t="n">
-        <v>485764.04</v>
+        <v>488968.63</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>43724</v>
+        <v>43719</v>
       </c>
     </row>
     <row r="14">
@@ -747,10 +747,10 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>63152.96</v>
+        <v>62249.42</v>
       </c>
       <c r="F14" t="n">
-        <v>41477.52</v>
+        <v>41053.34</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>43717</v>
@@ -769,13 +769,13 @@
         <v>184</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E15" t="n">
-        <v>812607.16</v>
+        <v>812136.9399999999</v>
       </c>
       <c r="F15" t="n">
-        <v>540940.45</v>
+        <v>536883.63</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>43752</v>
@@ -797,13 +797,13 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>62329.34</v>
+        <v>62750.19</v>
       </c>
       <c r="F16" t="n">
-        <v>39724</v>
+        <v>40086.96</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>43746</v>
+        <v>43748</v>
       </c>
     </row>
     <row r="17">
@@ -822,13 +822,13 @@
         <v>88</v>
       </c>
       <c r="E17" t="n">
-        <v>1023592.45</v>
+        <v>1021875.5</v>
       </c>
       <c r="F17" t="n">
-        <v>702263.15</v>
+        <v>698050.39</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>43780</v>
+        <v>43782</v>
       </c>
     </row>
     <row r="18">
@@ -847,10 +847,10 @@
         <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>70419.25999999999</v>
+        <v>72191.35000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>45501.12</v>
+        <v>46157.71</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>43780</v>
@@ -869,13 +869,13 @@
         <v>272</v>
       </c>
       <c r="D19" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E19" t="n">
-        <v>1197165.53</v>
+        <v>1198676.35</v>
       </c>
       <c r="F19" t="n">
-        <v>800190.36</v>
+        <v>798959.27</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>43811</v>
@@ -897,13 +897,13 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>90188.57000000001</v>
+        <v>89372.98</v>
       </c>
       <c r="F20" t="n">
-        <v>61392.95</v>
+        <v>59498.73</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>43809</v>
+        <v>43810</v>
       </c>
     </row>
     <row r="21">
@@ -919,13 +919,13 @@
         <v>269</v>
       </c>
       <c r="D21" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E21" t="n">
-        <v>1179906.79</v>
+        <v>1180490.41</v>
       </c>
       <c r="F21" t="n">
-        <v>807187.1</v>
+        <v>803203.74</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>43839</v>
@@ -947,13 +947,13 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>82674.39</v>
+        <v>81701.58</v>
       </c>
       <c r="F22" t="n">
-        <v>57337.23</v>
+        <v>56769.35</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>43838</v>
+        <v>43844</v>
       </c>
     </row>
     <row r="23">
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="E23" t="n">
-        <v>9386816.380000001</v>
+        <v>9384825.539999999</v>
       </c>
       <c r="F23" t="n">
-        <v>6166738.03</v>
+        <v>6143520.58</v>
       </c>
     </row>
   </sheetData>
